--- a/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 14:39</t>
+          <t>4/5/2026 14:18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 14:18</t>
+          <t>4/5/2026 13:47</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -510,22 +510,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 13:33</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 13:04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
     </row>
@@ -574,22 +574,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 15:20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:39</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 12:31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 12:33</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 08:19</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,17 +700,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 15:41</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 15:18</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:03</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:27</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 13:50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 14:54</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 13:35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:26</t>
+          <t>4/5/2026 14:29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:59</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
     </row>
@@ -912,27 +912,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>4/5/2026 15:22</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:42</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Infeed Station 3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>4/5/2026 08:40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Transport Cart 2</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:40</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Infeed Station 3</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:41</t>
         </is>
       </c>
     </row>
@@ -944,32 +944,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:46</t>
+          <t>4/5/2026 06:17</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:43</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:04</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 10:47</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:32</t>
+          <t>4/5/2026 10:26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 11:15</t>
+          <t>4/5/2026 11:02</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:42</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 13:51</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:57</t>
+          <t>4/5/2026 15:04</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 14:50</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:40</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -1129,17 +1129,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 14:16</t>
+          <t>4/5/2026 15:22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:10</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:29</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:17</t>
+          <t>4/5/2026 14:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 13:56</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.00/0.00/6.00 min</t>
+          <t>2.00/4.00/2.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170949 / 6418</t>
+          <t>162549 / 6218</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.3810 sec</t>
+          <t>0.3340 sec</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14.79</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="32">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12.68</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="35">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7.06</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="36">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="37">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.01</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="38">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38.51</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="39">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21.4</v>
+        <v>25.68</v>
       </c>
     </row>
   </sheetData>
@@ -2924,29 +2924,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>17</v>

--- a/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
@@ -468,17 +468,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 14:18</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 13:47</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
     </row>
@@ -505,27 +505,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:33</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
     </row>
@@ -537,22 +537,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 13:04</t>
+          <t>4/5/2026 12:10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 06:04</t>
         </is>
       </c>
     </row>
@@ -574,32 +574,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:20</t>
+          <t>4/5/2026 14:24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
     </row>
@@ -611,32 +611,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 12:31</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 12:33</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
     </row>
@@ -685,32 +685,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 14:59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 14:50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 15:18</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
     </row>
@@ -722,32 +722,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 10:26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
     </row>
@@ -764,27 +764,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:25</t>
+          <t>4/5/2026 15:08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 13:50</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -811,17 +811,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 12:38</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:35</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:29</t>
+          <t>4/5/2026 14:39</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 14:43</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 13:54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:42</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
     </row>
@@ -949,27 +949,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 12:05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 12:01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:17</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:07</t>
+          <t>4/5/2026 14:20</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 14:52</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 11:02</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 10:22</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:51</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:41</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:57</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
     </row>
@@ -1129,32 +1129,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 15:09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:59</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 15:08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:09</t>
+          <t>4/5/2026 14:36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 14:00</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:56</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.00/4.00/2.00 min</t>
+          <t>0.00/2.00/6.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>162549 / 6218</t>
+          <t>157110 / 6130</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.3340 sec</t>
+          <t>0.9540 sec</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25.35</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="32">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10.56</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="33">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.11</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="35">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.03</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="36">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.02</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="37">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.53</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="38">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>34.23</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="39">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25.68</v>
+        <v>29.95</v>
       </c>
     </row>
   </sheetData>
@@ -1977,16 +1977,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>6</v>
@@ -2924,42 +2924,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>4/5/2026 09:02</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:02</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>4/5/2026 09:04</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:08</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>4/5/2026 09:10</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:10</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
         <v>17</v>

--- a/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_1_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.9540 sec</t>
+          <t>0.9490 sec</t>
         </is>
       </c>
     </row>
